--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MINNESOTA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MINNESOTA_2013.xlsx
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C126">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C150">
@@ -7465,7 +7465,7 @@
         <v>69</v>
       </c>
       <c r="D395">
-        <v>0.009838870668758</v>
+        <v>0.009838870668758002</v>
       </c>
     </row>
     <row r="396">
@@ -9103,7 +9103,7 @@
         <v>65</v>
       </c>
       <c r="D486">
-        <v>0.009268501354627</v>
+        <v>0.009268501354627002</v>
       </c>
     </row>
     <row r="487">
@@ -9157,7 +9157,7 @@
         <v>65</v>
       </c>
       <c r="D489">
-        <v>0.009268501354627</v>
+        <v>0.009268501354627002</v>
       </c>
     </row>
     <row r="490">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C524">
@@ -17167,7 +17167,7 @@
         <v>65</v>
       </c>
       <c r="D934">
-        <v>0.009268501354627</v>
+        <v>0.009268501354627002</v>
       </c>
     </row>
     <row r="935">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C964">
